--- a/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 22,92</t>
+          <t>-5,01; 18,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 14,9</t>
+          <t>-6,07; 13,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,04; -3,25</t>
+          <t>-27,34; -3,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,35</t>
+          <t>-2,56; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 6,55</t>
+          <t>-11,0; 6,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,9</t>
+          <t>0,0; 14,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 8,04</t>
+          <t>-15,11; 8,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 19,87</t>
+          <t>-15,92; 18,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 19,91</t>
+          <t>-10,39; 20,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,62</t>
+          <t>0,0; 28,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,07; 0,0</t>
+          <t>-32,66; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 11,9</t>
+          <t>-4,16; 12,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 9,82</t>
+          <t>-5,5; 9,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,47</t>
+          <t>-3,8; 6,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 2,51</t>
+          <t>-8,73; 3,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,32; —</t>
+          <t>-100,0; 616,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 3,28</t>
+          <t>-21,34; 2,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 0,0</t>
+          <t>-16,31; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 0,0</t>
+          <t>-16,69; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 15,24</t>
+          <t>-35,14; 14,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,93</t>
+          <t>0,0; 39,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 0,0</t>
+          <t>-39,51; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 0,0</t>
+          <t>-30,02; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 3,75</t>
+          <t>-6,69; 3,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,13</t>
+          <t>-2,91; 4,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,34</t>
+          <t>-7,29; 0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,07</t>
+          <t>-4,56; 1,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 88,29</t>
+          <t>-64,91; 83,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-65,68; 297,51</t>
+          <t>-55,56; 276,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-93,2; 29,85</t>
+          <t>-92,99; 25,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-94,23; 93,23</t>
+          <t>-92,17; 91,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 18,66</t>
+          <t>-3,32; 18,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 13,17</t>
+          <t>-6,55; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,34; -3,24</t>
+          <t>-25,28; -3,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 5,61</t>
+          <t>-2,63; 6,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 6,53</t>
+          <t>-10,89; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,05</t>
+          <t>0,0; 14,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 8,06</t>
+          <t>-15,05; 8,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 18,66</t>
+          <t>-14,41; 20,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 20,7</t>
+          <t>-10,4; 20,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,64</t>
+          <t>0,0; 22,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 0,0</t>
+          <t>-33,47; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 12,08</t>
+          <t>-4,12; 11,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 9,51</t>
+          <t>-5,41; 9,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,38</t>
+          <t>-3,56; 7,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 3,01</t>
+          <t>-8,48; 2,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 616,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 2,09</t>
+          <t>-22,59; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 0,0</t>
+          <t>-14,54; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 0,0</t>
+          <t>-16,4; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 14,27</t>
+          <t>-37,12; 16,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,56</t>
+          <t>0,0; 39,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 0,0</t>
+          <t>-40,11; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 0,0</t>
+          <t>-32,68; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,7</t>
+          <t>-5,88; 3,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,92</t>
+          <t>-2,58; 5,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,01</t>
+          <t>-7,77; -0,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,26</t>
+          <t>-5,21; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 83,48</t>
+          <t>-62,41; 89,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,56; 276,8</t>
+          <t>-53,42; 308,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-92,99; 25,22</t>
+          <t>-94,15; 25,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 91,79</t>
+          <t>-89,28; 105,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 18,78</t>
+          <t>-2,93; 22,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 13,67</t>
+          <t>-5,61; 14,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,28; -3,17</t>
+          <t>-28,04; -3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 6,41</t>
+          <t>-2,35; 4,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 6,48</t>
+          <t>-11,28; 6,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,69</t>
+          <t>0,0; 13,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 8,2</t>
+          <t>-17,98; 8,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-11,13</t>
+          <t>-8,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 20,65</t>
+          <t>-14,55; 19,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 20,37</t>
+          <t>-10,62; 19,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,8</t>
+          <t>0,0; 22,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 0,0</t>
+          <t>-28,24; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-51,27%</t>
+          <t>-12,98%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 11,68</t>
+          <t>-4,17; 11,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 9,77</t>
+          <t>-5,15; 9,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 7,23</t>
+          <t>-5,22; 6,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 2,63</t>
+          <t>-6,76; 6,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,32; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 3,39</t>
+          <t>-22,64; 3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 0,0</t>
+          <t>-14,65; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 0,0</t>
+          <t>-16,93; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 13,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,57</t>
+          <t>-10,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 16,13</t>
+          <t>-37,06; 15,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,67</t>
+          <t>0,0; 49,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 0,0</t>
+          <t>-44,69; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 0,0</t>
+          <t>-33,1; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-51,31%</t>
+          <t>-42,08%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,81</t>
+          <t>-6,34; 3,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 5,13</t>
+          <t>-3,09; 5,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,77; -0,09</t>
+          <t>-7,84; 0,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,05</t>
+          <t>-4,36; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 89,77</t>
+          <t>-62,71; 88,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 308,31</t>
+          <t>-65,68; 297,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-94,15; 25,38</t>
+          <t>-93,2; 29,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-89,28; 105,55</t>
+          <t>-94,26; 125,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>151,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32,96%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.4197340514972625</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5956279911518543</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.83049439988225</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.09150205687693574</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.6619842799102972</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.8189440174521795</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3459541419590113</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 22,92</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,61; 14,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-28,04; -3,25</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,35; 4,77</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.40392812549402</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.588117456045165</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.967512320605482</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.5412068157077242</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.144423149915624</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.355327359389736</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.5860176619067217</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.298217911394723</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,58</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-48,56%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,28; 6,55</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,9</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-17,98; 8,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>-0.03714461189261156</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7833042600742246</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.8158107997507019</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.04973267637841198</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.6547253264446142</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-8,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.295508354002279</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.949038025273952</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-14,55; 19,87</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-10,62; 19,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 22,62</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-28,24; 0,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.461414800000106</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.197527533733728</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.431569954520828</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +783,173 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-12,98%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.4891307418179159</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06955206764644146</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7354592603614065</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.201926011854796</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2285002491115307</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.09331819538055626</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 11,9</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 9,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,22; 6,47</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,76; 6,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-85,32; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.641663806737088</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.518744920072763</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.664403427765631</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.822285529971592</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.725405690552365</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.994458950787383</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,51</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-71,87%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-22,64; 3,28</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-14,65; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-16,93; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.5839487884355287</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4589416492551075</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3777814141158399</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.1678774665347054</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8590944991284917</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4074351499094779</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1.349504427119736</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1595987764298322</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-11,54</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-15,3</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-10,4</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-58,35%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7890925360936598</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.391515362705656</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.2820153082633637</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.703596339282847</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.870222923136807</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-37,06; 15,24</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,93</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-44,69; 0,0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-33,1; 0,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.494080128505888</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.303460136714955</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.966753523287179</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.543734861351828</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>7.08833525007644</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,44 +957,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,37</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-17,07%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-63,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-42,08%</t>
+      <c r="C16" s="5" t="n">
+        <v>-1.620868707579242</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.9386703549793478</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6229646526481674</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.5475474094204408</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.7287393556147889</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -1255,52 +988,238 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-6,34; 3,75</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 5,13</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-7,84; 0,34</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-4,36; 1,51</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-62,71; 88,29</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-65,68; 297,51</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-93,2; 29,85</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-94,26; 125,68</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.527563013748186</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.220523984810866</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.109724224392368</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.5939109322767797</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.020365644592253</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-2.274208747121456</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.258281712850614</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-2.206366425019207</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-2.149823963146683</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.7341825547104346</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-7.686264519400606</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-6.689232535355845</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-6.550665583831675</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.7385396054877578</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.331486532083922</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.401151153055607</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.2427298354240371</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.520486698802184</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.332261781730483</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.279263430837006</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.3346262614404571</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.5948855825741793</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.4427733400660617</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.423149808851434</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6549247063614703</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.231289096185135</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.001794219421286</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.7284308892852566</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.6118195915018813</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.9078395452487675</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.9085223524939932</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.5747136480138288</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.041142248620152</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.05469055835595399</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.3572371673702179</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.645981171953566</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3.351829652812856</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.5331846076165025</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.313482508538867</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1227,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
